--- a/research/traditional_assets/database/data/new_zealand/new_zealand_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_precious_metals.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>-0.452</v>
+        <v>-3.31</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,70 +612,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.661</v>
+        <v>0.548</v>
       </c>
       <c r="V2">
-        <v>0.1029595015576324</v>
+        <v>0.1353086419753086</v>
       </c>
       <c r="W2">
-        <v>-0.04388349514563106</v>
+        <v>-0.3152380952380953</v>
       </c>
       <c r="X2">
-        <v>0.05479497789386831</v>
+        <v>0.1108572269125864</v>
       </c>
       <c r="Y2">
-        <v>-0.09867847303949936</v>
+        <v>-0.4260953221506817</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-0.05022075055187638</v>
+        <v>-0.3254769921436587</v>
       </c>
       <c r="AB2">
-        <v>0.05460893325211379</v>
+        <v>0.110905538078959</v>
       </c>
       <c r="AC2">
-        <v>-0.1048296838039902</v>
+        <v>-0.4363825302226177</v>
       </c>
       <c r="AD2">
-        <v>0.037</v>
+        <v>0.585</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.037</v>
+        <v>0.585</v>
       </c>
       <c r="AG2">
-        <v>-0.624</v>
+        <v>0.03699999999999992</v>
       </c>
       <c r="AH2">
-        <v>0.005730215270249341</v>
+        <v>0.1262135922330097</v>
       </c>
       <c r="AI2">
-        <v>0.003511435892569042</v>
+        <v>0.09709543568464729</v>
       </c>
       <c r="AJ2">
-        <v>-0.1076604554865424</v>
+        <v>0.009053095179838494</v>
       </c>
       <c r="AK2">
-        <v>-0.06318347509113001</v>
+        <v>0.006755523096585708</v>
       </c>
       <c r="AL2">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="AN2">
-        <v>-0.08525345622119815</v>
+        <v>-1.093457943925233</v>
       </c>
       <c r="AO2">
-        <v>-455</v>
+        <v>-531.6666666666666</v>
       </c>
       <c r="AP2">
-        <v>1.43778801843318</v>
+        <v>-0.06915887850467274</v>
+      </c>
+      <c r="AQ2">
+        <v>-638</v>
       </c>
     </row>
     <row r="3">
@@ -695,7 +698,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-0.452</v>
+        <v>-3.31</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -719,70 +722,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.661</v>
+        <v>0.548</v>
       </c>
       <c r="V3">
-        <v>0.1029595015576324</v>
+        <v>0.1353086419753086</v>
       </c>
       <c r="W3">
-        <v>-0.04388349514563106</v>
+        <v>-0.3152380952380953</v>
       </c>
       <c r="X3">
-        <v>0.05479497789386831</v>
+        <v>0.1108572269125864</v>
       </c>
       <c r="Y3">
-        <v>-0.09867847303949936</v>
+        <v>-0.4260953221506817</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.05022075055187638</v>
+        <v>-0.3254769921436587</v>
       </c>
       <c r="AB3">
-        <v>0.05460893325211379</v>
+        <v>0.110905538078959</v>
       </c>
       <c r="AC3">
-        <v>-0.1048296838039902</v>
+        <v>-0.4363825302226177</v>
       </c>
       <c r="AD3">
-        <v>0.037</v>
+        <v>0.585</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.037</v>
+        <v>0.585</v>
       </c>
       <c r="AG3">
-        <v>-0.624</v>
+        <v>0.03699999999999992</v>
       </c>
       <c r="AH3">
-        <v>0.005730215270249341</v>
+        <v>0.1262135922330097</v>
       </c>
       <c r="AI3">
-        <v>0.003511435892569042</v>
+        <v>0.09709543568464729</v>
       </c>
       <c r="AJ3">
-        <v>-0.1076604554865424</v>
+        <v>0.009053095179838494</v>
       </c>
       <c r="AK3">
-        <v>-0.06318347509113001</v>
+        <v>0.006755523096585708</v>
       </c>
       <c r="AL3">
-        <v>0.001</v>
+        <v>0.006</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="AN3">
-        <v>-0.08525345622119815</v>
+        <v>-1.093457943925233</v>
       </c>
       <c r="AO3">
-        <v>-455</v>
+        <v>-531.6666666666666</v>
       </c>
       <c r="AP3">
-        <v>1.43778801843318</v>
+        <v>-0.06915887850467274</v>
+      </c>
+      <c r="AQ3">
+        <v>-638</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/new_zealand/new_zealand_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_precious_metals.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>-3.31</v>
+        <v>-1.51</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,73 +612,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.548</v>
+        <v>0.966</v>
       </c>
       <c r="V2">
-        <v>0.1353086419753086</v>
+        <v>0.1645655877342419</v>
       </c>
       <c r="W2">
-        <v>-0.3152380952380953</v>
+        <v>-0.2775735294117647</v>
       </c>
       <c r="X2">
-        <v>0.1108572269125864</v>
+        <v>0.08994209323520586</v>
       </c>
       <c r="Y2">
-        <v>-0.4260953221506817</v>
+        <v>-0.3675156226469705</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-0.3254769921436587</v>
+        <v>-0.2983383685800604</v>
       </c>
       <c r="AB2">
-        <v>0.110905538078959</v>
+        <v>0.08768070692579304</v>
       </c>
       <c r="AC2">
-        <v>-0.4363825302226177</v>
+        <v>-0.3860190755058535</v>
       </c>
       <c r="AD2">
-        <v>0.585</v>
+        <v>0.603</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.585</v>
+        <v>0.603</v>
       </c>
       <c r="AG2">
-        <v>0.03699999999999992</v>
+        <v>-0.363</v>
       </c>
       <c r="AH2">
-        <v>0.1262135922330097</v>
+        <v>0.09315618723930172</v>
       </c>
       <c r="AI2">
-        <v>0.09709543568464729</v>
+        <v>0.0975254730713246</v>
       </c>
       <c r="AJ2">
-        <v>0.009053095179838494</v>
+        <v>-0.06591610677319774</v>
       </c>
       <c r="AK2">
-        <v>0.006755523096585708</v>
+        <v>-0.06958021851638872</v>
       </c>
       <c r="AL2">
-        <v>0.006</v>
+        <v>0.059</v>
       </c>
       <c r="AM2">
-        <v>0.005</v>
+        <v>0.04099999999999999</v>
       </c>
       <c r="AN2">
-        <v>-1.093457943925233</v>
+        <v>-1.269473684210526</v>
       </c>
       <c r="AO2">
-        <v>-531.6666666666666</v>
+        <v>-26.77966101694916</v>
       </c>
       <c r="AP2">
-        <v>-0.06915887850467274</v>
+        <v>0.7642105263157895</v>
       </c>
       <c r="AQ2">
-        <v>-638</v>
+        <v>-38.53658536585367</v>
       </c>
     </row>
     <row r="3">
@@ -698,7 +698,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-3.31</v>
+        <v>-1.51</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -722,73 +722,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.548</v>
+        <v>0.966</v>
       </c>
       <c r="V3">
-        <v>0.1353086419753086</v>
+        <v>0.1645655877342419</v>
       </c>
       <c r="W3">
-        <v>-0.3152380952380953</v>
+        <v>-0.2775735294117647</v>
       </c>
       <c r="X3">
-        <v>0.1108572269125864</v>
+        <v>0.08994209323520586</v>
       </c>
       <c r="Y3">
-        <v>-0.4260953221506817</v>
+        <v>-0.3675156226469705</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.3254769921436587</v>
+        <v>-0.2983383685800604</v>
       </c>
       <c r="AB3">
-        <v>0.110905538078959</v>
+        <v>0.08768070692579304</v>
       </c>
       <c r="AC3">
-        <v>-0.4363825302226177</v>
+        <v>-0.3860190755058535</v>
       </c>
       <c r="AD3">
-        <v>0.585</v>
+        <v>0.603</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.585</v>
+        <v>0.603</v>
       </c>
       <c r="AG3">
-        <v>0.03699999999999992</v>
+        <v>-0.363</v>
       </c>
       <c r="AH3">
-        <v>0.1262135922330097</v>
+        <v>0.09315618723930172</v>
       </c>
       <c r="AI3">
-        <v>0.09709543568464729</v>
+        <v>0.0975254730713246</v>
       </c>
       <c r="AJ3">
-        <v>0.009053095179838494</v>
+        <v>-0.06591610677319774</v>
       </c>
       <c r="AK3">
-        <v>0.006755523096585708</v>
+        <v>-0.06958021851638872</v>
       </c>
       <c r="AL3">
-        <v>0.006</v>
+        <v>0.059</v>
       </c>
       <c r="AM3">
-        <v>0.005</v>
+        <v>0.04099999999999999</v>
       </c>
       <c r="AN3">
-        <v>-1.093457943925233</v>
+        <v>-1.269473684210526</v>
       </c>
       <c r="AO3">
-        <v>-531.6666666666666</v>
+        <v>-26.77966101694916</v>
       </c>
       <c r="AP3">
-        <v>-0.06915887850467274</v>
+        <v>0.7642105263157895</v>
       </c>
       <c r="AQ3">
-        <v>-638</v>
+        <v>-38.53658536585367</v>
       </c>
     </row>
   </sheetData>
